--- a/database/event/3486/event_3486_evp_summary.xlsx
+++ b/database/event/3486/event_3486_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.0659</v>
+        <v>12.0506</v>
       </c>
       <c r="C2" t="n">
-        <v>7.5502</v>
+        <v>7.5407</v>
       </c>
       <c r="D2" t="n">
-        <v>4.453</v>
+        <v>4.3571</v>
       </c>
       <c r="E2" t="n">
-        <v>12.0659</v>
+        <v>12.0506</v>
       </c>
       <c r="F2" t="n">
-        <v>5.5806</v>
+        <v>5.5652</v>
       </c>
       <c r="G2" t="n">
         <v>6.4853</v>
       </c>
       <c r="H2" t="n">
-        <v>6.4473</v>
+        <v>6.4232</v>
       </c>
       <c r="I2" t="n">
         <v>6.4773</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.521000000000001</v>
+        <v>9.4963</v>
       </c>
       <c r="C3" t="n">
-        <v>5.9578</v>
+        <v>5.9423</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4249</v>
+        <v>3.3394</v>
       </c>
       <c r="E3" t="n">
-        <v>9.521000000000001</v>
+        <v>9.4963</v>
       </c>
       <c r="F3" t="n">
-        <v>4.7743</v>
+        <v>4.7496</v>
       </c>
       <c r="G3" t="n">
         <v>4.7467</v>
       </c>
       <c r="H3" t="n">
-        <v>5.183</v>
+        <v>5.1444</v>
       </c>
       <c r="I3" t="n">
         <v>5.2313</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.723100000000001</v>
+        <v>8.695600000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>5.4585</v>
+        <v>5.4413</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1026</v>
+        <v>3.0204</v>
       </c>
       <c r="E4" t="n">
-        <v>8.723100000000001</v>
+        <v>8.695600000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>5.1588</v>
+        <v>5.1314</v>
       </c>
       <c r="G4" t="n">
         <v>3.5643</v>
       </c>
       <c r="H4" t="n">
-        <v>5.786</v>
+        <v>5.7429</v>
       </c>
       <c r="I4" t="n">
         <v>5.84</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.343500000000001</v>
+        <v>8.3147</v>
       </c>
       <c r="C5" t="n">
-        <v>5.2209</v>
+        <v>5.2029</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9492</v>
+        <v>2.8687</v>
       </c>
       <c r="E5" t="n">
-        <v>8.343500000000001</v>
+        <v>8.3147</v>
       </c>
       <c r="F5" t="n">
-        <v>3.8691</v>
+        <v>3.8403</v>
       </c>
       <c r="G5" t="n">
         <v>4.4745</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8691</v>
+        <v>3.8403</v>
       </c>
       <c r="I5" t="n">
         <v>3.9052</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.8613</v>
+        <v>6.8486</v>
       </c>
       <c r="C6" t="n">
-        <v>4.2935</v>
+        <v>4.2855</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3505</v>
+        <v>2.2846</v>
       </c>
       <c r="E6" t="n">
-        <v>6.8613</v>
+        <v>6.8486</v>
       </c>
       <c r="F6" t="n">
-        <v>4.8955</v>
+        <v>4.8828</v>
       </c>
       <c r="G6" t="n">
         <v>1.9658</v>
       </c>
       <c r="H6" t="n">
-        <v>5.3731</v>
+        <v>5.3531</v>
       </c>
       <c r="I6" t="n">
         <v>5.3982</v>
@@ -732,7 +732,7 @@
         <v>4.0415</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1878</v>
+        <v>2.1292</v>
       </c>
       <c r="E7" t="n">
         <v>6.4587</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.8554</v>
+        <v>5.8403</v>
       </c>
       <c r="C8" t="n">
-        <v>3.664</v>
+        <v>3.6546</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9441</v>
+        <v>1.8829</v>
       </c>
       <c r="E8" t="n">
-        <v>5.8554</v>
+        <v>5.8403</v>
       </c>
       <c r="F8" t="n">
-        <v>5.5218</v>
+        <v>5.5067</v>
       </c>
       <c r="G8" t="n">
         <v>0.3336</v>
       </c>
       <c r="H8" t="n">
-        <v>6.3552</v>
+        <v>6.3314</v>
       </c>
       <c r="I8" t="n">
         <v>6.3847</v>
@@ -824,7 +824,7 @@
         <v>3.6118</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9104</v>
+        <v>1.8556</v>
       </c>
       <c r="E9" t="n">
         <v>5.7719</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.6768</v>
+        <v>5.6625</v>
       </c>
       <c r="C10" t="n">
-        <v>3.5523</v>
+        <v>3.5433</v>
       </c>
       <c r="D10" t="n">
-        <v>1.8719</v>
+        <v>1.812</v>
       </c>
       <c r="E10" t="n">
-        <v>5.6768</v>
+        <v>5.6625</v>
       </c>
       <c r="F10" t="n">
-        <v>5.3015</v>
+        <v>5.2872</v>
       </c>
       <c r="G10" t="n">
         <v>0.3753</v>
       </c>
       <c r="H10" t="n">
-        <v>6.0096</v>
+        <v>5.9872</v>
       </c>
       <c r="I10" t="n">
         <v>6.0376</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.6297</v>
+        <v>5.6225</v>
       </c>
       <c r="C11" t="n">
-        <v>3.5228</v>
+        <v>3.5183</v>
       </c>
       <c r="D11" t="n">
-        <v>1.8529</v>
+        <v>1.7961</v>
       </c>
       <c r="E11" t="n">
-        <v>5.6297</v>
+        <v>5.6225</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9186</v>
+        <v>1.9115</v>
       </c>
       <c r="G11" t="n">
         <v>3.7111</v>
       </c>
       <c r="H11" t="n">
-        <v>1.9186</v>
+        <v>1.9115</v>
       </c>
       <c r="I11" t="n">
         <v>1.9276</v>
@@ -962,7 +962,7 @@
         <v>3.2622</v>
       </c>
       <c r="D12" t="n">
-        <v>1.6847</v>
+        <v>1.633</v>
       </c>
       <c r="E12" t="n">
         <v>5.2132</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.182</v>
+        <v>5.1721</v>
       </c>
       <c r="C13" t="n">
-        <v>3.2426</v>
+        <v>3.2364</v>
       </c>
       <c r="D13" t="n">
-        <v>1.6721</v>
+        <v>1.6167</v>
       </c>
       <c r="E13" t="n">
-        <v>5.182</v>
+        <v>5.1721</v>
       </c>
       <c r="F13" t="n">
-        <v>4.106</v>
+        <v>4.0961</v>
       </c>
       <c r="G13" t="n">
         <v>1.076</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1351</v>
+        <v>4.1197</v>
       </c>
       <c r="I13" t="n">
         <v>4.1543</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.0948</v>
+        <v>5.0836</v>
       </c>
       <c r="C14" t="n">
-        <v>3.1881</v>
+        <v>3.1811</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6368</v>
+        <v>1.5814</v>
       </c>
       <c r="E14" t="n">
-        <v>5.0948</v>
+        <v>5.0836</v>
       </c>
       <c r="F14" t="n">
-        <v>4.4854</v>
+        <v>4.4742</v>
       </c>
       <c r="G14" t="n">
         <v>0.6094000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>4.7301</v>
+        <v>4.7125</v>
       </c>
       <c r="I14" t="n">
         <v>4.7521</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.8859</v>
+        <v>4.8711</v>
       </c>
       <c r="C15" t="n">
-        <v>3.0573</v>
+        <v>3.0481</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5524</v>
+        <v>1.4967</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8859</v>
+        <v>4.8711</v>
       </c>
       <c r="F15" t="n">
-        <v>3.966</v>
+        <v>3.9512</v>
       </c>
       <c r="G15" t="n">
         <v>0.9199000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>3.966</v>
+        <v>3.9512</v>
       </c>
       <c r="I15" t="n">
         <v>3.9844</v>
@@ -1146,7 +1146,7 @@
         <v>2.9493</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4827</v>
+        <v>1.4339</v>
       </c>
       <c r="E16" t="n">
         <v>4.7133</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.4991</v>
+        <v>4.4881</v>
       </c>
       <c r="C17" t="n">
-        <v>2.8153</v>
+        <v>2.8084</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3962</v>
+        <v>1.3441</v>
       </c>
       <c r="E17" t="n">
-        <v>4.4991</v>
+        <v>4.4881</v>
       </c>
       <c r="F17" t="n">
-        <v>4.4215</v>
+        <v>4.4105</v>
       </c>
       <c r="G17" t="n">
         <v>0.0776</v>
       </c>
       <c r="H17" t="n">
-        <v>4.6299</v>
+        <v>4.6126</v>
       </c>
       <c r="I17" t="n">
         <v>4.6514</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.3546</v>
+        <v>4.3447</v>
       </c>
       <c r="C18" t="n">
-        <v>2.7249</v>
+        <v>2.7187</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3378</v>
+        <v>1.287</v>
       </c>
       <c r="E18" t="n">
-        <v>4.3546</v>
+        <v>4.3447</v>
       </c>
       <c r="F18" t="n">
-        <v>4.1344</v>
+        <v>4.1245</v>
       </c>
       <c r="G18" t="n">
         <v>0.2202</v>
       </c>
       <c r="H18" t="n">
-        <v>4.1797</v>
+        <v>4.1641</v>
       </c>
       <c r="I18" t="n">
         <v>4.1992</v>
@@ -1284,7 +1284,7 @@
         <v>2.6395</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2827</v>
+        <v>1.2366</v>
       </c>
       <c r="E19" t="n">
         <v>4.2182</v>
@@ -1330,7 +1330,7 @@
         <v>2.612</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2649</v>
+        <v>1.2191</v>
       </c>
       <c r="E20" t="n">
         <v>4.1742</v>
@@ -1376,7 +1376,7 @@
         <v>2.545</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2217</v>
+        <v>1.1764</v>
       </c>
       <c r="E21" t="n">
         <v>4.0671</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.9937</v>
+        <v>3.9825</v>
       </c>
       <c r="C22" t="n">
-        <v>2.4991</v>
+        <v>2.492</v>
       </c>
       <c r="D22" t="n">
-        <v>1.192</v>
+        <v>1.1427</v>
       </c>
       <c r="E22" t="n">
-        <v>3.9937</v>
+        <v>3.9825</v>
       </c>
       <c r="F22" t="n">
-        <v>4.4626</v>
+        <v>4.4514</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4689</v>
       </c>
       <c r="H22" t="n">
-        <v>4.6943</v>
+        <v>4.6768</v>
       </c>
       <c r="I22" t="n">
         <v>4.7162</v>
@@ -1468,7 +1468,7 @@
         <v>2.0785</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9205</v>
+        <v>0.8794</v>
       </c>
       <c r="E23" t="n">
         <v>3.3216</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.2868</v>
+        <v>3.2763</v>
       </c>
       <c r="C24" t="n">
-        <v>2.0567</v>
+        <v>2.0501</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9064</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>3.2868</v>
+        <v>3.2763</v>
       </c>
       <c r="F24" t="n">
-        <v>2.8209</v>
+        <v>2.8104</v>
       </c>
       <c r="G24" t="n">
         <v>0.4659</v>
       </c>
       <c r="H24" t="n">
-        <v>2.8209</v>
+        <v>2.8104</v>
       </c>
       <c r="I24" t="n">
         <v>2.834</v>
@@ -1560,7 +1560,7 @@
         <v>2.0433</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8978</v>
+        <v>0.857</v>
       </c>
       <c r="E25" t="n">
         <v>3.2654</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.1887</v>
+        <v>3.1833</v>
       </c>
       <c r="C26" t="n">
-        <v>1.9953</v>
+        <v>1.9919</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8668</v>
+        <v>0.8243</v>
       </c>
       <c r="E26" t="n">
-        <v>3.1887</v>
+        <v>3.1833</v>
       </c>
       <c r="F26" t="n">
-        <v>1.4439</v>
+        <v>1.4385</v>
       </c>
       <c r="G26" t="n">
         <v>1.7448</v>
       </c>
       <c r="H26" t="n">
-        <v>1.4439</v>
+        <v>1.4385</v>
       </c>
       <c r="I26" t="n">
         <v>1.4506</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.0269</v>
+        <v>3.0142</v>
       </c>
       <c r="C27" t="n">
-        <v>1.8941</v>
+        <v>1.8861</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8014</v>
+        <v>0.7569</v>
       </c>
       <c r="E27" t="n">
-        <v>3.0269</v>
+        <v>3.0142</v>
       </c>
       <c r="F27" t="n">
-        <v>3.3887</v>
+        <v>3.376</v>
       </c>
       <c r="G27" t="n">
         <v>-0.3618</v>
       </c>
       <c r="H27" t="n">
-        <v>3.3887</v>
+        <v>3.376</v>
       </c>
       <c r="I27" t="n">
         <v>3.4044</v>
@@ -1688,93 +1688,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.5039</v>
+        <v>2.5022</v>
       </c>
       <c r="C28" t="n">
-        <v>1.5668</v>
+        <v>1.5657</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.553</v>
       </c>
       <c r="E28" t="n">
-        <v>2.5039</v>
+        <v>2.5022</v>
       </c>
       <c r="F28" t="n">
-        <v>1.0378</v>
+        <v>2.5022</v>
       </c>
       <c r="G28" t="n">
-        <v>1.4661</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.0378</v>
+        <v>2.5022</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0426</v>
+        <v>2.5022</v>
       </c>
       <c r="J28" t="n">
-        <v>1.4661</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>334</v>
+        <v>194</v>
       </c>
       <c r="L28" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.5087</v>
+        <v>2.5022</v>
       </c>
       <c r="N28" t="n">
-        <v>574</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.5022</v>
+        <v>2.5</v>
       </c>
       <c r="C29" t="n">
-        <v>1.5657</v>
+        <v>1.5644</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5895</v>
+        <v>0.5521</v>
       </c>
       <c r="E29" t="n">
-        <v>2.5022</v>
+        <v>2.5</v>
       </c>
       <c r="F29" t="n">
-        <v>2.5022</v>
+        <v>1.0339</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="H29" t="n">
-        <v>2.5022</v>
+        <v>1.0339</v>
       </c>
       <c r="I29" t="n">
-        <v>2.5022</v>
+        <v>1.0426</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="K29" t="n">
-        <v>194</v>
+        <v>334</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="M29" t="n">
-        <v>2.5022</v>
+        <v>2.5087</v>
       </c>
       <c r="N29" t="n">
-        <v>194</v>
+        <v>574</v>
       </c>
     </row>
     <row r="30">
@@ -1790,7 +1790,7 @@
         <v>1.5415</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5738</v>
+        <v>0.5375</v>
       </c>
       <c r="E30" t="n">
         <v>2.4634</v>
@@ -1836,7 +1836,7 @@
         <v>1.4643</v>
       </c>
       <c r="D31" t="n">
-        <v>0.524</v>
+        <v>0.4884</v>
       </c>
       <c r="E31" t="n">
         <v>2.3401</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.2412</v>
+        <v>2.2345</v>
       </c>
       <c r="C32" t="n">
-        <v>1.4024</v>
+        <v>1.3982</v>
       </c>
       <c r="D32" t="n">
-        <v>0.484</v>
+        <v>0.4463</v>
       </c>
       <c r="E32" t="n">
-        <v>2.2412</v>
+        <v>2.2345</v>
       </c>
       <c r="F32" t="n">
-        <v>1.8024</v>
+        <v>1.7957</v>
       </c>
       <c r="G32" t="n">
         <v>0.4388</v>
       </c>
       <c r="H32" t="n">
-        <v>1.8024</v>
+        <v>1.7957</v>
       </c>
       <c r="I32" t="n">
         <v>1.8108</v>
@@ -1928,7 +1928,7 @@
         <v>1.1732</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3361</v>
+        <v>0.3031</v>
       </c>
       <c r="E33" t="n">
         <v>1.8749</v>
@@ -1974,7 +1974,7 @@
         <v>1.1441</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3172</v>
+        <v>0.2845</v>
       </c>
       <c r="E34" t="n">
         <v>1.8283</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.626</v>
+        <v>1.6162</v>
       </c>
       <c r="C35" t="n">
-        <v>1.0175</v>
+        <v>1.0113</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2355</v>
+        <v>0.2</v>
       </c>
       <c r="E35" t="n">
-        <v>1.626</v>
+        <v>1.6162</v>
       </c>
       <c r="F35" t="n">
-        <v>1.3175</v>
+        <v>1.3077</v>
       </c>
       <c r="G35" t="n">
         <v>0.3085</v>
       </c>
       <c r="H35" t="n">
-        <v>1.3175</v>
+        <v>1.3077</v>
       </c>
       <c r="I35" t="n">
         <v>1.3298</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.4125</v>
+        <v>1.4041</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8839</v>
+        <v>0.8786</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1493</v>
+        <v>0.1155</v>
       </c>
       <c r="E36" t="n">
-        <v>1.4125</v>
+        <v>1.4041</v>
       </c>
       <c r="F36" t="n">
-        <v>2.2374</v>
+        <v>2.229</v>
       </c>
       <c r="G36" t="n">
         <v>-0.8249</v>
       </c>
       <c r="H36" t="n">
-        <v>2.2374</v>
+        <v>2.229</v>
       </c>
       <c r="I36" t="n">
         <v>2.2478</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.3218</v>
+        <v>1.3141</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.8223</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1126</v>
+        <v>0.0796</v>
       </c>
       <c r="E37" t="n">
-        <v>1.3218</v>
+        <v>1.3141</v>
       </c>
       <c r="F37" t="n">
-        <v>2.0583</v>
+        <v>2.0506</v>
       </c>
       <c r="G37" t="n">
         <v>-0.7365</v>
       </c>
       <c r="H37" t="n">
-        <v>2.0583</v>
+        <v>2.0506</v>
       </c>
       <c r="I37" t="n">
         <v>2.0679</v>
@@ -2158,7 +2158,7 @@
         <v>0.8222</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1095</v>
+        <v>0.0796</v>
       </c>
       <c r="E38" t="n">
         <v>1.314</v>
@@ -2204,7 +2204,7 @@
         <v>0.7008</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0311</v>
+        <v>0.0023</v>
       </c>
       <c r="E39" t="n">
         <v>1.1199</v>
@@ -2250,7 +2250,7 @@
         <v>0.6973</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0288</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>1.1143</v>
@@ -2296,7 +2296,7 @@
         <v>0.6563</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0024</v>
+        <v>-0.026</v>
       </c>
       <c r="E41" t="n">
         <v>1.0489</v>
@@ -2342,7 +2342,7 @@
         <v>0.62</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0211</v>
+        <v>-0.0492</v>
       </c>
       <c r="E42" t="n">
         <v>0.9908</v>
@@ -2388,7 +2388,7 @@
         <v>0.6175</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.0227</v>
+        <v>-0.0508</v>
       </c>
       <c r="E43" t="n">
         <v>0.9868</v>
@@ -2434,7 +2434,7 @@
         <v>0.5666</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.0556</v>
+        <v>-0.0832</v>
       </c>
       <c r="E44" t="n">
         <v>0.9054</v>
@@ -2480,7 +2480,7 @@
         <v>0.4937</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1026</v>
+        <v>-0.1296</v>
       </c>
       <c r="E45" t="n">
         <v>0.789</v>
@@ -2526,7 +2526,7 @@
         <v>0.4076</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1583</v>
+        <v>-0.1844</v>
       </c>
       <c r="E46" t="n">
         <v>0.6513</v>
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5638</v>
+        <v>0.5596</v>
       </c>
       <c r="C47" t="n">
-        <v>0.3528</v>
+        <v>0.3502</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1936</v>
+        <v>-0.221</v>
       </c>
       <c r="E47" t="n">
-        <v>0.5638</v>
+        <v>0.5596</v>
       </c>
       <c r="F47" t="n">
-        <v>0.5625</v>
+        <v>0.5583</v>
       </c>
       <c r="G47" t="n">
         <v>0.0013</v>
       </c>
       <c r="H47" t="n">
-        <v>0.5625</v>
+        <v>0.5583</v>
       </c>
       <c r="I47" t="n">
         <v>0.5677</v>
@@ -2618,7 +2618,7 @@
         <v>0.3049</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2245</v>
+        <v>-0.2498</v>
       </c>
       <c r="E48" t="n">
         <v>0.4872</v>
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4683</v>
+        <v>0.4646</v>
       </c>
       <c r="C49" t="n">
-        <v>0.293</v>
+        <v>0.2907</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2322</v>
+        <v>-0.2588</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4683</v>
+        <v>0.4646</v>
       </c>
       <c r="F49" t="n">
-        <v>1.0052</v>
+        <v>1.0015</v>
       </c>
       <c r="G49" t="n">
         <v>-0.5369</v>
       </c>
       <c r="H49" t="n">
-        <v>1.0052</v>
+        <v>1.0015</v>
       </c>
       <c r="I49" t="n">
         <v>1.0099</v>
@@ -2710,7 +2710,7 @@
         <v>0.263</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.2516</v>
+        <v>-0.2765</v>
       </c>
       <c r="E50" t="n">
         <v>0.4203</v>
@@ -2756,7 +2756,7 @@
         <v>0.2235</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.2771</v>
+        <v>-0.3016</v>
       </c>
       <c r="E51" t="n">
         <v>0.3571</v>
@@ -2802,7 +2802,7 @@
         <v>0.0506</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3887</v>
+        <v>-0.4117</v>
       </c>
       <c r="E52" t="n">
         <v>0.0809</v>
@@ -2848,7 +2848,7 @@
         <v>0.0244</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4056</v>
+        <v>-0.4284</v>
       </c>
       <c r="E53" t="n">
         <v>0.039</v>
@@ -2894,7 +2894,7 @@
         <v>-0.0382</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.446</v>
+        <v>-0.4682</v>
       </c>
       <c r="E54" t="n">
         <v>-0.061</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.1121</v>
+        <v>-0.1106</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0701</v>
+        <v>-0.0692</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4666</v>
+        <v>-0.488</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.1121</v>
+        <v>-0.1106</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.4045</v>
+        <v>-0.403</v>
       </c>
       <c r="G55" t="n">
         <v>0.2924</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.4045</v>
+        <v>-0.403</v>
       </c>
       <c r="I55" t="n">
         <v>-0.4064</v>
@@ -2986,7 +2986,7 @@
         <v>-0.1516</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5192</v>
+        <v>-0.5404</v>
       </c>
       <c r="E56" t="n">
         <v>-0.2422</v>
@@ -3032,7 +3032,7 @@
         <v>-0.2104</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5572</v>
+        <v>-0.5779</v>
       </c>
       <c r="E57" t="n">
         <v>-0.3363</v>
@@ -3078,7 +3078,7 @@
         <v>-0.2797</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6019</v>
+        <v>-0.622</v>
       </c>
       <c r="E58" t="n">
         <v>-0.447</v>
@@ -3124,7 +3124,7 @@
         <v>-0.3014</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.616</v>
+        <v>-0.6358</v>
       </c>
       <c r="E59" t="n">
         <v>-0.4817</v>
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.5696</v>
+        <v>-0.5689</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.3564</v>
+        <v>-0.356</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6515</v>
+        <v>-0.6706</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.5696</v>
+        <v>-0.5689</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.1611</v>
+        <v>-0.1604</v>
       </c>
       <c r="G60" t="n">
         <v>-0.4085</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.1611</v>
+        <v>-0.1604</v>
       </c>
       <c r="I60" t="n">
         <v>-0.1618</v>
@@ -3216,7 +3216,7 @@
         <v>-0.3918</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6743</v>
+        <v>-0.6933</v>
       </c>
       <c r="E61" t="n">
         <v>-0.6261</v>
@@ -3256,25 +3256,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.6533</v>
+        <v>-0.6534</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.4088</v>
+        <v>-0.4089</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6853</v>
+        <v>-0.7042</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.6533</v>
+        <v>-0.6534</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0265</v>
+        <v>0.0264</v>
       </c>
       <c r="G62" t="n">
         <v>-0.6798</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0265</v>
+        <v>0.0264</v>
       </c>
       <c r="I62" t="n">
         <v>0.0266</v>
@@ -3308,7 +3308,7 @@
         <v>-0.4339</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7015</v>
+        <v>-0.7202</v>
       </c>
       <c r="E63" t="n">
         <v>-0.6934</v>
@@ -3354,7 +3354,7 @@
         <v>-0.4918</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7389</v>
+        <v>-0.7571</v>
       </c>
       <c r="E64" t="n">
         <v>-0.786</v>
@@ -3400,7 +3400,7 @@
         <v>-0.5372</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7682</v>
+        <v>-0.7859</v>
       </c>
       <c r="E65" t="n">
         <v>-0.8585</v>
@@ -3446,7 +3446,7 @@
         <v>-0.594</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8048</v>
+        <v>-0.8221000000000001</v>
       </c>
       <c r="E66" t="n">
         <v>-0.9492</v>
@@ -3492,7 +3492,7 @@
         <v>-0.6067</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8131</v>
+        <v>-0.8302</v>
       </c>
       <c r="E67" t="n">
         <v>-0.9696</v>
@@ -3532,25 +3532,25 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.2058</v>
+        <v>-1.2051</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.7544999999999999</v>
+        <v>-0.7541</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9085</v>
+        <v>-0.924</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.2058</v>
+        <v>-1.2051</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.2058</v>
+        <v>-0.2051</v>
       </c>
       <c r="G68" t="n">
         <v>-1</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.2058</v>
+        <v>-0.2051</v>
       </c>
       <c r="I68" t="n">
         <v>-0.2068</v>
@@ -3584,7 +3584,7 @@
         <v>-0.8328</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.959</v>
+        <v>-0.9741</v>
       </c>
       <c r="E69" t="n">
         <v>-1.3309</v>
@@ -3630,7 +3630,7 @@
         <v>-0.8333</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9593</v>
+        <v>-0.9745</v>
       </c>
       <c r="E70" t="n">
         <v>-1.3317</v>
@@ -3676,7 +3676,7 @@
         <v>-0.9051</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0057</v>
+        <v>-1.0202</v>
       </c>
       <c r="E71" t="n">
         <v>-1.4464</v>
@@ -3722,7 +3722,7 @@
         <v>-1.0717</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.1133</v>
+        <v>-1.1263</v>
       </c>
       <c r="E72" t="n">
         <v>-1.7127</v>
@@ -3768,7 +3768,7 @@
         <v>-1.1325</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.1525</v>
+        <v>-1.165</v>
       </c>
       <c r="E73" t="n">
         <v>-1.8099</v>
@@ -3814,7 +3814,7 @@
         <v>-1.2083</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.2014</v>
+        <v>-1.2132</v>
       </c>
       <c r="E74" t="n">
         <v>-1.931</v>
@@ -3860,7 +3860,7 @@
         <v>-1.2336</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.2178</v>
+        <v>-1.2293</v>
       </c>
       <c r="E75" t="n">
         <v>-1.9714</v>
@@ -3906,7 +3906,7 @@
         <v>-1.3797</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.3121</v>
+        <v>-1.3223</v>
       </c>
       <c r="E76" t="n">
         <v>-2.2049</v>
@@ -3952,7 +3952,7 @@
         <v>-1.4049</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.3284</v>
+        <v>-1.3384</v>
       </c>
       <c r="E77" t="n">
         <v>-2.2452</v>
@@ -3998,7 +3998,7 @@
         <v>-1.4767</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.3747</v>
+        <v>-1.3841</v>
       </c>
       <c r="E78" t="n">
         <v>-2.3599</v>
@@ -4044,7 +4044,7 @@
         <v>-1.4953</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.3867</v>
+        <v>-1.3959</v>
       </c>
       <c r="E79" t="n">
         <v>-2.3896</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.4259</v>
+        <v>-2.4212</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.518</v>
+        <v>-1.5151</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.4014</v>
+        <v>-1.4085</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.4259</v>
+        <v>-2.4212</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.2671</v>
+        <v>-1.2624</v>
       </c>
       <c r="G80" t="n">
         <v>-1.1588</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.2671</v>
+        <v>-1.2624</v>
       </c>
       <c r="I80" t="n">
         <v>-1.273</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.8774</v>
+        <v>-2.8717</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.8005</v>
+        <v>-1.797</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.5838</v>
+        <v>-1.588</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.8774</v>
+        <v>-2.8717</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.5379</v>
+        <v>-1.5322</v>
       </c>
       <c r="G81" t="n">
         <v>-1.3395</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.5379</v>
+        <v>-1.5322</v>
       </c>
       <c r="I81" t="n">
         <v>-1.545</v>
@@ -4182,7 +4182,7 @@
         <v>-2.8259</v>
       </c>
       <c r="D82" t="n">
-        <v>-2.2457</v>
+        <v>-2.2431</v>
       </c>
       <c r="E82" t="n">
         <v>-4.516</v>
